--- a/backend/tests/fixtures/sample_import.xlsx
+++ b/backend/tests/fixtures/sample_import.xlsx
@@ -1146,7 +1146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1264,17 +1264,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>contingency</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>12500</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -1283,23 +1283,23 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>marketing</t>
+          <t>infrastructure</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5000</v>
+        <v>20000</v>
       </c>
       <c r="C6" t="n">
-        <v>7500</v>
+        <v>30000</v>
       </c>
       <c r="D6" t="n">
-        <v>12500</v>
+        <v>50000</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -1308,23 +1308,23 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>25000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>admin_overheads</t>
+          <t>professional_fees</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -1333,257 +1333,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>infrastructure</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>20000</v>
-      </c>
-      <c r="C8" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D8" t="n">
         <v>50000</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>civil_works</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>landscaping</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>amenities</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>professional_fees</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>10000</v>
-      </c>
-      <c r="C12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D12" t="n">
-        <v>25000</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>regulatory_fees</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>contingency_civil_works</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>contingency_amenities</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>ancillary_build_capex</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
